--- a/artfynd/A 27771-2024 artfynd.xlsx
+++ b/artfynd/A 27771-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118852252</v>
+        <v>118852218</v>
       </c>
       <c r="B2" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476997</v>
+        <v>477223</v>
       </c>
       <c r="R2" t="n">
-        <v>7039425</v>
+        <v>7039621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118852253</v>
+        <v>118852219</v>
       </c>
       <c r="B3" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477044</v>
+        <v>477250</v>
       </c>
       <c r="R3" t="n">
-        <v>7039470</v>
+        <v>7038920</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118852219</v>
+        <v>118852261</v>
       </c>
       <c r="B4" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477250</v>
+        <v>477291</v>
       </c>
       <c r="R4" t="n">
-        <v>7038920</v>
+        <v>7039650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118852248</v>
+        <v>118852262</v>
       </c>
       <c r="B5" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477156</v>
+        <v>477267</v>
       </c>
       <c r="R5" t="n">
-        <v>7039544</v>
+        <v>7039493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118852257</v>
+        <v>118852263</v>
       </c>
       <c r="B6" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477233</v>
+        <v>477209</v>
       </c>
       <c r="R6" t="n">
-        <v>7038922</v>
+        <v>7039201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118852249</v>
+        <v>118852264</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477138</v>
+        <v>477038</v>
       </c>
       <c r="R7" t="n">
-        <v>7039677</v>
+        <v>7039365</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118852242</v>
+        <v>118852265</v>
       </c>
       <c r="B8" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477278</v>
+        <v>477092</v>
       </c>
       <c r="R8" t="n">
-        <v>7039417</v>
+        <v>7039675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,50 +1354,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118852244</v>
+        <v>118852221</v>
       </c>
       <c r="B9" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477336</v>
+        <v>477170</v>
       </c>
       <c r="R9" t="n">
-        <v>7039256</v>
+        <v>7039687</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,6 +1429,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,50 +1460,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118852240</v>
+        <v>118852222</v>
       </c>
       <c r="B10" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477261</v>
+        <v>477252</v>
       </c>
       <c r="R10" t="n">
-        <v>7039634</v>
+        <v>7039490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1535,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,50 +1566,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118852239</v>
+        <v>118852223</v>
       </c>
       <c r="B11" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477228</v>
+        <v>477227</v>
       </c>
       <c r="R11" t="n">
-        <v>7039598</v>
+        <v>7039415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,6 +1641,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,50 +1672,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118852243</v>
+        <v>118852224</v>
       </c>
       <c r="B12" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477295</v>
+        <v>477343</v>
       </c>
       <c r="R12" t="n">
-        <v>7039405</v>
+        <v>7039330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1747,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,15 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118852261</v>
+        <v>118852225</v>
       </c>
       <c r="B13" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1789,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477291</v>
+        <v>477348</v>
       </c>
       <c r="R13" t="n">
-        <v>7039650</v>
+        <v>7039323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,15 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118852263</v>
+        <v>118852226</v>
       </c>
       <c r="B14" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,34 +1895,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477209</v>
+        <v>477044</v>
       </c>
       <c r="R14" t="n">
-        <v>7039201</v>
+        <v>7039470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,6 +1963,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål drygt 2m upp i toppbruten gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,15 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118852265</v>
+        <v>118852227</v>
       </c>
       <c r="B15" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,34 +2005,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477092</v>
+        <v>477127</v>
       </c>
       <c r="R15" t="n">
-        <v>7039675</v>
+        <v>7039517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2069,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,50 +2100,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118852247</v>
+        <v>118852228</v>
       </c>
       <c r="B16" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477004</v>
+        <v>477393</v>
       </c>
       <c r="R16" t="n">
-        <v>7039468</v>
+        <v>7038847</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,12 +2169,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,50 +2206,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118852241</v>
+        <v>118852229</v>
       </c>
       <c r="B17" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477224</v>
+        <v>477283</v>
       </c>
       <c r="R17" t="n">
-        <v>7039461</v>
+        <v>7038928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,12 +2275,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,50 +2312,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118852234</v>
+        <v>118852230</v>
       </c>
       <c r="B18" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477146</v>
+        <v>477550</v>
       </c>
       <c r="R18" t="n">
-        <v>7039321</v>
+        <v>7039096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,12 +2381,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,50 +2418,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118852236</v>
+        <v>115175035</v>
       </c>
       <c r="B19" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
+          <t>Krokbodarna NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477115</v>
+        <v>476909</v>
       </c>
       <c r="R19" t="n">
-        <v>7039689</v>
+        <v>7039600</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,12 +2483,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,12 +2518,7 @@
         <v>118852250</v>
       </c>
       <c r="B20" t="n">
-        <v>97757</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,15 +2612,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118852245</v>
+        <v>118852239</v>
       </c>
       <c r="B21" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2653,10 +2647,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477244</v>
+        <v>477228</v>
       </c>
       <c r="R21" t="n">
-        <v>7039148</v>
+        <v>7039598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,37 +2709,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118852218</v>
+        <v>118852240</v>
       </c>
       <c r="B22" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477223</v>
+        <v>477261</v>
       </c>
       <c r="R22" t="n">
-        <v>7039621</v>
+        <v>7039634</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,37 +2806,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118852264</v>
+        <v>118852241</v>
       </c>
       <c r="B23" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2841,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477038</v>
+        <v>477224</v>
       </c>
       <c r="R23" t="n">
-        <v>7039365</v>
+        <v>7039461</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,37 +2903,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118852259</v>
+        <v>118852242</v>
       </c>
       <c r="B24" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2938,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477610</v>
+        <v>477278</v>
       </c>
       <c r="R24" t="n">
-        <v>7039046</v>
+        <v>7039417</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,12 +2968,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,37 +3000,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118852256</v>
+        <v>118852243</v>
       </c>
       <c r="B25" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477410</v>
+        <v>477295</v>
       </c>
       <c r="R25" t="n">
-        <v>7038863</v>
+        <v>7039405</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,12 +3065,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,37 +3097,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118852262</v>
+        <v>118852244</v>
       </c>
       <c r="B26" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477267</v>
+        <v>477336</v>
       </c>
       <c r="R26" t="n">
-        <v>7039493</v>
+        <v>7039256</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,37 +3194,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118852255</v>
+        <v>118852245</v>
       </c>
       <c r="B27" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477405</v>
+        <v>477244</v>
       </c>
       <c r="R27" t="n">
-        <v>7038836</v>
+        <v>7039148</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,12 +3259,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3327,37 +3291,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118852258</v>
+        <v>118852246</v>
       </c>
       <c r="B28" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477295</v>
+        <v>477004</v>
       </c>
       <c r="R28" t="n">
-        <v>7039027</v>
+        <v>7039383</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,12 +3356,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3429,37 +3388,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118852254</v>
+        <v>118852247</v>
       </c>
       <c r="B29" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3423,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477531</v>
+        <v>477004</v>
       </c>
       <c r="R29" t="n">
-        <v>7038975</v>
+        <v>7039468</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,12 +3453,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3531,37 +3485,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118852251</v>
+        <v>118852248</v>
       </c>
       <c r="B30" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3520,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477273</v>
+        <v>477156</v>
       </c>
       <c r="R30" t="n">
-        <v>7039500</v>
+        <v>7039544</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,37 +3582,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118852235</v>
+        <v>118852249</v>
       </c>
       <c r="B31" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3617,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477161</v>
+        <v>477138</v>
       </c>
       <c r="R31" t="n">
-        <v>7039579</v>
+        <v>7039677</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,37 +3679,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118852246</v>
+        <v>118852234</v>
       </c>
       <c r="B32" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3714,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477004</v>
+        <v>477146</v>
       </c>
       <c r="R32" t="n">
-        <v>7039383</v>
+        <v>7039321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,54 +3776,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118852228</v>
+        <v>118852235</v>
       </c>
       <c r="B33" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477393</v>
+        <v>477161</v>
       </c>
       <c r="R33" t="n">
-        <v>7038847</v>
+        <v>7039579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,17 +3841,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3948,54 +3873,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118852221</v>
+        <v>118852236</v>
       </c>
       <c r="B34" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477170</v>
+        <v>477115</v>
       </c>
       <c r="R34" t="n">
-        <v>7039687</v>
+        <v>7039689</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4030,11 +3946,6 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4056,898 +3967,6 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>118852225</v>
-      </c>
-      <c r="B35" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>477348</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7039323</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>118852229</v>
-      </c>
-      <c r="B36" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>477283</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7038928</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>118852227</v>
-      </c>
-      <c r="B37" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>477127</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7039517</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>118852223</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>477227</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7039415</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>118852230</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>477550</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7039096</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>118852222</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>477252</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7039490</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>118852224</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>477343</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7039330</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>118852226</v>
-      </c>
-      <c r="B42" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Krokbodarna NÖ - Ö.gpx, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>477044</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7039470</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Bohål drygt 2m upp i toppbruten gran</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27771-2024 artfynd.xlsx
+++ b/artfynd/A 27771-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852218</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852219</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852261</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852262</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852263</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852264</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852265</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852221</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852222</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852223</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852224</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852225</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852226</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,6 +2167,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852227</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852228</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852229</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852230</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115175035</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852250</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852239</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852240</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852241</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2997,6 +3112,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852242</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3094,6 +3214,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852243</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3191,6 +3316,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852244</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3288,6 +3418,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852245</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3385,6 +3520,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852246</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3482,6 +3622,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852247</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3579,6 +3724,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852248</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3676,6 +3826,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852249</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3773,6 +3928,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852234</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3870,6 +4030,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852235</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3967,8 +4132,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118852236</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>